--- a/Sigmoid_Intern_TOC_DE (1).xlsx
+++ b/Sigmoid_Intern_TOC_DE (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\om\Desktop\DE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AE1BB13-E45A-46B9-A949-F8250C4C4F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{471AD989-2E67-4EF7-8706-BD1B477F2DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{AE212680-33AA-4B7F-A746-5552D9AC5729}"/>
   </bookViews>
@@ -4025,6 +4025,24 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4043,15 +4061,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4061,20 +4070,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4296,7 +4296,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I969"/>
+  <dimension ref="A1:I971"/>
   <sheetFormatPr defaultColWidth="91" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
@@ -4448,13 +4448,13 @@
       <c r="C6" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="D6" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="38"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
       <c r="I6" s="14"/>
     </row>
     <row r="7" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
@@ -4467,11 +4467,11 @@
       <c r="C7" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
       <c r="I7" s="14"/>
     </row>
     <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
@@ -4484,13 +4484,13 @@
       <c r="C8" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="D8" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
       <c r="I8" s="14"/>
     </row>
     <row r="9" spans="1:9" ht="409.6" x14ac:dyDescent="0.25">
@@ -4603,13 +4603,13 @@
       <c r="C13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="38" t="s">
+      <c r="D13" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="38"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
       <c r="I13" s="14"/>
     </row>
     <row r="14" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
@@ -4622,11 +4622,11 @@
       <c r="C14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="38"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
       <c r="I14" s="14"/>
     </row>
     <row r="15" spans="1:9" ht="409.6" x14ac:dyDescent="0.25">
@@ -4764,13 +4764,13 @@
       <c r="C20" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="38" t="s">
+      <c r="D20" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
       <c r="I20" s="14"/>
     </row>
     <row r="21" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
@@ -4783,11 +4783,11 @@
       <c r="C21" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
       <c r="I21" s="14"/>
     </row>
     <row r="22" spans="1:9" ht="409.6" x14ac:dyDescent="0.25">
@@ -4841,17 +4841,17 @@
       <c r="I23" s="14"/>
     </row>
     <row r="24" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A24" s="39" t="s">
+      <c r="A24" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="B24" s="39"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="39"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="39"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="27"/>
     </row>
     <row r="25" spans="1:9" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
@@ -4975,7 +4975,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="3" t="str">
-        <f t="shared" ref="C29:C60" si="0">TEXT(A29,"dddd")</f>
+        <f t="shared" ref="C29:C62" si="0">TEXT(A29,"dddd")</f>
         <v>Friday</v>
       </c>
       <c r="D29" s="3" t="s">
@@ -5007,11 +5007,11 @@
       <c r="D30" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E30" s="32" t="s">
+      <c r="E30" s="29" t="s">
         <v>144</v>
       </c>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
       <c r="H30" s="13"/>
       <c r="I30" s="13"/>
     </row>
@@ -5029,9 +5029,9 @@
       <c r="D31" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E31" s="32"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="32"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
       <c r="H31" s="1"/>
       <c r="I31" s="3"/>
     </row>
@@ -5099,14 +5099,14 @@
         <f t="shared" si="0"/>
         <v>Wednesday</v>
       </c>
-      <c r="D34" s="40" t="s">
+      <c r="D34" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="E34" s="41"/>
-      <c r="F34" s="41"/>
-      <c r="G34" s="41"/>
-      <c r="H34" s="41"/>
-      <c r="I34" s="41"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="31"/>
+      <c r="H34" s="31"/>
+      <c r="I34" s="31"/>
     </row>
     <row r="35" spans="1:9" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
@@ -5136,138 +5136,104 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="343.2" x14ac:dyDescent="0.25">
-      <c r="A36" s="4">
-        <v>46108</v>
-      </c>
-      <c r="B36" s="14">
+    <row r="36" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A36" s="4"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+    </row>
+    <row r="37" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A37" s="4"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+    </row>
+    <row r="38" spans="1:9" ht="343.2" x14ac:dyDescent="0.25">
+      <c r="A38" s="4">
+        <v>46111</v>
+      </c>
+      <c r="B38" s="14">
         <v>34</v>
       </c>
-      <c r="C36" s="3" t="str">
+      <c r="C38" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>Friday</v>
-      </c>
-      <c r="D36" s="3" t="s">
+        <v>Monday</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E38" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="F38" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="G38" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H36" s="16" t="s">
+      <c r="H38" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="I36" s="3"/>
-    </row>
-    <row r="37" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="4">
+      <c r="I38" s="3"/>
+    </row>
+    <row r="39" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="4">
         <v>46109</v>
       </c>
-      <c r="B37" s="14">
+      <c r="B39" s="14">
         <v>35</v>
       </c>
-      <c r="C37" s="3" t="str">
+      <c r="C39" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D39" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E37" s="32" t="s">
+      <c r="E39" s="29" t="s">
         <v>144</v>
       </c>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-    </row>
-    <row r="38" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A38" s="4">
+      <c r="F39" s="29"/>
+      <c r="G39" s="29"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+    </row>
+    <row r="40" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A40" s="4">
         <v>46110</v>
       </c>
-      <c r="B38" s="14">
+      <c r="B40" s="14">
         <v>36</v>
       </c>
-      <c r="C38" s="3" t="str">
+      <c r="C40" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Sunday</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" s="32"/>
-      <c r="F38" s="32"/>
-      <c r="G38" s="32"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="3"/>
-    </row>
-    <row r="39" spans="1:9" ht="312" x14ac:dyDescent="0.25">
-      <c r="A39" s="42">
-        <v>46111</v>
-      </c>
-      <c r="B39" s="14">
-        <v>37</v>
-      </c>
-      <c r="C39" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Monday</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H39" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="I39" s="3"/>
-    </row>
-    <row r="40" spans="1:9" ht="312" x14ac:dyDescent="0.25">
-      <c r="A40" s="4">
-        <v>46112</v>
-      </c>
-      <c r="B40" s="14">
-        <v>38</v>
-      </c>
-      <c r="C40" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Tuesday</v>
-      </c>
       <c r="D40" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E40" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="H40" s="16" t="s">
-        <v>83</v>
-      </c>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="1"/>
       <c r="I40" s="3"/>
     </row>
     <row r="41" spans="1:9" ht="312" x14ac:dyDescent="0.25">
-      <c r="A41" s="4">
+      <c r="A41" s="26">
         <v>46113</v>
       </c>
       <c r="B41" s="14">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C41" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5277,25 +5243,25 @@
         <v>8</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H41" s="16" t="s">
         <v>83</v>
       </c>
       <c r="I41" s="3"/>
     </row>
-    <row r="42" spans="1:9" ht="409.6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" ht="312" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>46114</v>
       </c>
       <c r="B42" s="14">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C42" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5305,25 +5271,25 @@
         <v>8</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="H42" s="16" t="s">
         <v>83</v>
       </c>
       <c r="I42" s="3"/>
     </row>
-    <row r="43" spans="1:9" ht="409.6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" ht="312" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>46115</v>
       </c>
       <c r="B43" s="14">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C43" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5333,20 +5299,18 @@
         <v>8</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="H43" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>103</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="H43" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="I43" s="3"/>
     </row>
     <row r="44" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
@@ -5356,17 +5320,17 @@
         <v>42</v>
       </c>
       <c r="C44" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT(A44,"dddd")</f>
         <v>Saturday</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E44" s="32" t="s">
+      <c r="E44" s="29" t="s">
         <v>144</v>
       </c>
-      <c r="F44" s="32"/>
-      <c r="G44" s="32"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="29"/>
       <c r="H44" s="13"/>
     </row>
     <row r="45" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
@@ -5377,15 +5341,15 @@
         <v>43</v>
       </c>
       <c r="C45" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT(A45,"dddd")</f>
         <v>Sunday</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="32"/>
-      <c r="F45" s="32"/>
-      <c r="G45" s="32"/>
+      <c r="E45" s="29"/>
+      <c r="F45" s="29"/>
+      <c r="G45" s="29"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
     </row>
@@ -5394,7 +5358,7 @@
         <v>46118</v>
       </c>
       <c r="B46" s="14">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C46" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5404,16 +5368,16 @@
         <v>8</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="H46" s="12" t="s">
-        <v>102</v>
+        <v>95</v>
+      </c>
+      <c r="H46" s="16" t="s">
+        <v>83</v>
       </c>
       <c r="I46" s="3"/>
     </row>
@@ -5422,7 +5386,7 @@
         <v>46119</v>
       </c>
       <c r="B47" s="14">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C47" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5432,17 +5396,19 @@
         <v>8</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="H47" s="15"/>
+        <v>101</v>
+      </c>
+      <c r="H47" s="12" t="s">
+        <v>102</v>
+      </c>
       <c r="I47" s="3" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="409.6" x14ac:dyDescent="0.25">
@@ -5450,7 +5416,7 @@
         <v>46120</v>
       </c>
       <c r="B48" s="14">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C48" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5460,27 +5426,25 @@
         <v>8</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>111</v>
+        <v>99</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>104</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="390" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+      <c r="I48" s="3"/>
+    </row>
+    <row r="49" spans="1:9" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>46121</v>
       </c>
       <c r="B49" s="14">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C49" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5490,25 +5454,25 @@
         <v>8</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>115</v>
+        <v>106</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>107</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="H49" s="1"/>
+        <v>108</v>
+      </c>
+      <c r="H49" s="15"/>
       <c r="I49" s="3" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="358.8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>46122</v>
       </c>
       <c r="B50" s="14">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C50" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5518,19 +5482,19 @@
         <v>8</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>148</v>
+        <v>110</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="H50" s="16" t="s">
-        <v>83</v>
+        <v>112</v>
+      </c>
+      <c r="H50" s="12" t="s">
+        <v>113</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -5541,17 +5505,17 @@
         <v>48</v>
       </c>
       <c r="C51" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT(A51,"dddd")</f>
         <v>Saturday</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E51" s="26" t="s">
+      <c r="E51" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="F51" s="27"/>
-      <c r="G51" s="28"/>
+      <c r="F51" s="33"/>
+      <c r="G51" s="34"/>
       <c r="H51" s="13"/>
       <c r="I51" s="13"/>
     </row>
@@ -5563,15 +5527,15 @@
         <v>49</v>
       </c>
       <c r="C52" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT(A52,"dddd")</f>
         <v>Sunday</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E52" s="29"/>
-      <c r="F52" s="30"/>
-      <c r="G52" s="31"/>
+      <c r="E52" s="35"/>
+      <c r="F52" s="36"/>
+      <c r="G52" s="37"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
     </row>
@@ -5583,28 +5547,28 @@
         <v>50</v>
       </c>
       <c r="C53" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT(A53,"dddd")</f>
         <v>Monday</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E53" s="35" t="s">
+      <c r="E53" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="F53" s="36"/>
-      <c r="G53" s="37"/>
+      <c r="F53" s="39"/>
+      <c r="G53" s="40"/>
       <c r="H53" s="16" t="s">
         <v>149</v>
       </c>
       <c r="I53" s="3"/>
     </row>
-    <row r="54" spans="1:9" ht="409.6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" ht="390" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>46126</v>
       </c>
       <c r="B54" s="14">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C54" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5614,25 +5578,25 @@
         <v>8</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="H54" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="I54" s="3"/>
-    </row>
-    <row r="55" spans="1:9" ht="409.6" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="H54" s="1"/>
+      <c r="I54" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="358.8" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>46127</v>
       </c>
       <c r="B55" s="14">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C55" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5642,25 +5606,27 @@
         <v>8</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="H55" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="I55" s="3"/>
-    </row>
-    <row r="56" spans="1:9" ht="31.2" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+      <c r="H55" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>46128</v>
       </c>
       <c r="B56" s="14">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C56" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5669,22 +5635,26 @@
       <c r="D56" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E56" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="F56" s="27"/>
-      <c r="G56" s="28"/>
+      <c r="E56" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>120</v>
+      </c>
       <c r="H56" s="12" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="I56" s="3"/>
     </row>
-    <row r="57" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>46129</v>
       </c>
       <c r="B57" s="14">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C57" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5693,10 +5663,18 @@
       <c r="D57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E57" s="29"/>
-      <c r="F57" s="30"/>
-      <c r="G57" s="31"/>
-      <c r="H57" s="1"/>
+      <c r="E57" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H57" s="12" t="s">
+        <v>121</v>
+      </c>
       <c r="I57" s="3"/>
     </row>
     <row r="58" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
@@ -5707,17 +5685,17 @@
         <v>55</v>
       </c>
       <c r="C58" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT(A58,"dddd")</f>
         <v>Saturday</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E58" s="26" t="s">
+      <c r="E58" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="F58" s="27"/>
-      <c r="G58" s="28"/>
+      <c r="F58" s="33"/>
+      <c r="G58" s="34"/>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
     </row>
@@ -5729,15 +5707,15 @@
         <v>56</v>
       </c>
       <c r="C59" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT(A59,"dddd")</f>
         <v>Sunday</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E59" s="29"/>
-      <c r="F59" s="30"/>
-      <c r="G59" s="31"/>
+      <c r="E59" s="35"/>
+      <c r="F59" s="36"/>
+      <c r="G59" s="37"/>
       <c r="H59" s="1"/>
       <c r="I59" s="3"/>
     </row>
@@ -5746,7 +5724,7 @@
         <v>46132</v>
       </c>
       <c r="B60" s="14">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C60" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5758,28 +5736,56 @@
       <c r="E60" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="F60" s="32"/>
-      <c r="G60" s="32"/>
+      <c r="F60" s="33"/>
+      <c r="G60" s="34"/>
       <c r="H60" s="12" t="s">
         <v>125</v>
       </c>
       <c r="I60" s="3"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="6"/>
-      <c r="B61" s="7"/>
-      <c r="C61" s="7"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-      <c r="G61" s="9"/>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="6"/>
-      <c r="B62" s="7"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-      <c r="G62" s="9"/>
+    <row r="61" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A61" s="4">
+        <v>46133</v>
+      </c>
+      <c r="B61" s="14">
+        <v>54</v>
+      </c>
+      <c r="C61" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" s="35"/>
+      <c r="F61" s="36"/>
+      <c r="G61" s="37"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="3"/>
+    </row>
+    <row r="62" spans="1:9" ht="31.2" x14ac:dyDescent="0.25">
+      <c r="A62" s="4">
+        <v>46134</v>
+      </c>
+      <c r="B62" s="14">
+        <v>57</v>
+      </c>
+      <c r="C62" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="F62" s="29"/>
+      <c r="G62" s="29"/>
+      <c r="H62" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="I62" s="3"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="6"/>
@@ -13037,22 +13043,38 @@
       <c r="E969" s="7"/>
       <c r="G969" s="9"/>
     </row>
+    <row r="970" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A970" s="6"/>
+      <c r="B970" s="7"/>
+      <c r="C970" s="7"/>
+      <c r="D970" s="7"/>
+      <c r="E970" s="7"/>
+      <c r="G970" s="9"/>
+    </row>
+    <row r="971" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A971" s="6"/>
+      <c r="B971" s="7"/>
+      <c r="C971" s="7"/>
+      <c r="D971" s="7"/>
+      <c r="E971" s="7"/>
+      <c r="G971" s="9"/>
+    </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="E30:G31"/>
+    <mergeCell ref="E39:G40"/>
+    <mergeCell ref="E44:G45"/>
+    <mergeCell ref="D34:I34"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="E51:G52"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="E60:G61"/>
+    <mergeCell ref="E58:G59"/>
     <mergeCell ref="A24:I24"/>
     <mergeCell ref="D6:H7"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="D13:H14"/>
     <mergeCell ref="D20:H21"/>
-    <mergeCell ref="E30:G31"/>
-    <mergeCell ref="E37:G38"/>
-    <mergeCell ref="E44:G45"/>
-    <mergeCell ref="D34:I34"/>
-    <mergeCell ref="E60:G60"/>
-    <mergeCell ref="E51:G52"/>
-    <mergeCell ref="E53:G53"/>
-    <mergeCell ref="E56:G57"/>
-    <mergeCell ref="E58:G59"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="I32" r:id="rId1" xr:uid="{62BA3F6F-3F84-4833-A300-A2BD55BD1E33}"/>
@@ -13221,13 +13243,13 @@
       <c r="C6" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="D6" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="38"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
       <c r="I6" s="14"/>
     </row>
     <row r="7" spans="1:9" ht="15.6" hidden="1" x14ac:dyDescent="0.25">
@@ -13240,11 +13262,11 @@
       <c r="C7" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
       <c r="I7" s="14"/>
     </row>
     <row r="8" spans="1:9" ht="15.6" hidden="1" x14ac:dyDescent="0.25">
@@ -13257,13 +13279,13 @@
       <c r="C8" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="D8" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
       <c r="I8" s="14"/>
     </row>
     <row r="9" spans="1:9" ht="409.6" hidden="1" x14ac:dyDescent="0.25">
@@ -13376,13 +13398,13 @@
       <c r="C13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="38" t="s">
+      <c r="D13" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="38"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
       <c r="I13" s="14"/>
     </row>
     <row r="14" spans="1:9" ht="15.6" hidden="1" x14ac:dyDescent="0.25">
@@ -13395,11 +13417,11 @@
       <c r="C14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="38"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
       <c r="I14" s="14"/>
     </row>
     <row r="15" spans="1:9" ht="409.6" hidden="1" x14ac:dyDescent="0.25">
@@ -13537,13 +13559,13 @@
       <c r="C20" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="38" t="s">
+      <c r="D20" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
       <c r="I20" s="14"/>
     </row>
     <row r="21" spans="1:9" ht="15.6" hidden="1" x14ac:dyDescent="0.25">
@@ -13556,11 +13578,11 @@
       <c r="C21" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
       <c r="I21" s="14"/>
     </row>
     <row r="22" spans="1:9" ht="409.6" hidden="1" x14ac:dyDescent="0.25">
@@ -13614,17 +13636,17 @@
       <c r="I23" s="14"/>
     </row>
     <row r="24" spans="1:9" ht="15.6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="39" t="s">
+      <c r="A24" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="B24" s="39"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="39"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="39"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="27"/>
     </row>
     <row r="25" spans="1:9" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
@@ -13778,11 +13800,11 @@
       <c r="D30" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E30" s="32" t="s">
+      <c r="E30" s="29" t="s">
         <v>144</v>
       </c>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
       <c r="H30" s="19"/>
       <c r="I30" s="19"/>
     </row>
@@ -13800,9 +13822,9 @@
       <c r="D31" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E31" s="32"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="32"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
       <c r="H31" s="1"/>
       <c r="I31" s="3"/>
     </row>
@@ -13871,14 +13893,14 @@
         <f t="shared" si="0"/>
         <v>Wednesday</v>
       </c>
-      <c r="D34" s="33" t="s">
+      <c r="D34" s="41" t="s">
         <v>78</v>
       </c>
-      <c r="E34" s="34"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="34"/>
-      <c r="H34" s="34"/>
-      <c r="I34" s="34"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
+      <c r="H34" s="42"/>
+      <c r="I34" s="42"/>
     </row>
     <row r="35" spans="1:9" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
@@ -13950,11 +13972,11 @@
       <c r="D37" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E37" s="32" t="s">
+      <c r="E37" s="29" t="s">
         <v>144</v>
       </c>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
       <c r="H37" s="19"/>
       <c r="I37" s="19"/>
     </row>
@@ -13972,9 +13994,9 @@
       <c r="D38" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E38" s="32"/>
-      <c r="F38" s="32"/>
-      <c r="G38" s="32"/>
+      <c r="E38" s="29"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
       <c r="H38" s="1"/>
       <c r="I38" s="3"/>
     </row>
@@ -14134,11 +14156,11 @@
       <c r="D44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E44" s="32" t="s">
+      <c r="E44" s="29" t="s">
         <v>144</v>
       </c>
-      <c r="F44" s="32"/>
-      <c r="G44" s="32"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="29"/>
       <c r="H44" s="19"/>
       <c r="I44" s="20"/>
     </row>
@@ -14156,9 +14178,9 @@
       <c r="D45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="32"/>
-      <c r="F45" s="32"/>
-      <c r="G45" s="32"/>
+      <c r="E45" s="29"/>
+      <c r="F45" s="29"/>
+      <c r="G45" s="29"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
     </row>
@@ -14318,11 +14340,11 @@
       <c r="D51" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E51" s="26" t="s">
+      <c r="E51" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="F51" s="27"/>
-      <c r="G51" s="28"/>
+      <c r="F51" s="33"/>
+      <c r="G51" s="34"/>
       <c r="H51" s="19"/>
       <c r="I51" s="19"/>
     </row>
@@ -14340,9 +14362,9 @@
       <c r="D52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E52" s="29"/>
-      <c r="F52" s="30"/>
-      <c r="G52" s="31"/>
+      <c r="E52" s="35"/>
+      <c r="F52" s="36"/>
+      <c r="G52" s="37"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
     </row>
@@ -14360,11 +14382,11 @@
       <c r="D53" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E53" s="35" t="s">
+      <c r="E53" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="F53" s="36"/>
-      <c r="G53" s="37"/>
+      <c r="F53" s="39"/>
+      <c r="G53" s="40"/>
       <c r="H53" s="16" t="s">
         <v>149</v>
       </c>
@@ -14440,11 +14462,11 @@
       <c r="D56" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E56" s="26" t="s">
+      <c r="E56" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="F56" s="27"/>
-      <c r="G56" s="28"/>
+      <c r="F56" s="33"/>
+      <c r="G56" s="34"/>
       <c r="H56" s="12" t="s">
         <v>143</v>
       </c>
@@ -14464,9 +14486,9 @@
       <c r="D57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E57" s="29"/>
-      <c r="F57" s="30"/>
-      <c r="G57" s="31"/>
+      <c r="E57" s="35"/>
+      <c r="F57" s="36"/>
+      <c r="G57" s="37"/>
       <c r="H57" s="1"/>
       <c r="I57" s="3"/>
     </row>
@@ -14484,11 +14506,11 @@
       <c r="D58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E58" s="26" t="s">
+      <c r="E58" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="F58" s="27"/>
-      <c r="G58" s="28"/>
+      <c r="F58" s="33"/>
+      <c r="G58" s="34"/>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
     </row>
@@ -14506,9 +14528,9 @@
       <c r="D59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E59" s="29"/>
-      <c r="F59" s="30"/>
-      <c r="G59" s="31"/>
+      <c r="E59" s="35"/>
+      <c r="F59" s="36"/>
+      <c r="G59" s="37"/>
       <c r="H59" s="1"/>
       <c r="I59" s="3"/>
     </row>
@@ -14526,11 +14548,11 @@
       <c r="D60" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E60" s="32" t="s">
+      <c r="E60" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="F60" s="32"/>
-      <c r="G60" s="32"/>
+      <c r="F60" s="29"/>
+      <c r="G60" s="29"/>
       <c r="H60" s="12" t="s">
         <v>143</v>
       </c>
@@ -21810,12 +21832,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="E30:G31"/>
-    <mergeCell ref="D6:H7"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D13:H14"/>
-    <mergeCell ref="D20:H21"/>
-    <mergeCell ref="A24:I24"/>
     <mergeCell ref="E58:G59"/>
     <mergeCell ref="E60:G60"/>
     <mergeCell ref="D34:I34"/>
@@ -21824,6 +21840,12 @@
     <mergeCell ref="E51:G52"/>
     <mergeCell ref="E53:G53"/>
     <mergeCell ref="E56:G57"/>
+    <mergeCell ref="E30:G31"/>
+    <mergeCell ref="D6:H7"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D13:H14"/>
+    <mergeCell ref="D20:H21"/>
+    <mergeCell ref="A24:I24"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="I32" r:id="rId1" xr:uid="{ED8495C0-C82A-4F99-A5AC-CAE92C83C6B8}"/>
